--- a/excel/锂.xlsx
+++ b/excel/锂.xlsx
@@ -660,10 +660,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V2" t="n">
+        <v>26787.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -672,7 +670,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>FY23(620kt)→FY24(725kt)靠 P680 初级抛废设施投产放量；FY25(754.6kt) 先升后降：2024年12月 Ngungaju 关停保养转向 Pilgan 单厂 P850 模式，2025Q1(日历年)叠加飓风/检修降至125kt，随后恢复；FY26 前三季连创新高（224.8→208.0→232.4kt），P1000 扩建支撑。</t>
+          <t>26Q2=FY26Q4 Pilgangoora 精矿 214,300 dmt（季度纪录；销量 249,900 dmt 纪录）×0.125=26,788 吨 LCE；FY26 879,500 吨（+17% 超指引）；P2000 预可研支出获批。源：PLS Q4 FY26 季报（7/29）</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -760,10 +758,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V3" t="n">
+        <v>22000</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -772,7 +768,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Wodgina FY23爬产(64→110kt/季)，FY24-FY25稳态~100-126kt/季，FY26量价齐升扩至156-176kt/季；Mt Marion FY24创纪录（峰值182kt/季）后FY25主动减产~22%应对低价，FY26回升。2025-11-12公告POSCO以US$765M收购持有两矿50%权益的LithCo 30%股权（MinRes保留70%并继续运营，预计2026下半年交割），矿山权益与披露未中断。</t>
+          <t>26Q2=FY26Q4：Wodgina 94k dmt + Mt Marion 82k dmt（季报口径）×0.125=22,000 吨 LCE；Bald Hill 5 月重启（首批 7 月发运）未计；FY26 锂 559k dmt SC6 全超指引。⚠️26Q1 存量值 39,500 与本口径不合（待核）。源：MinRes Q4 FY26 季报（7/29）</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -958,10 +954,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V5" t="n">
+        <v>84100</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -970,7 +964,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2023→2024销量17.0→20.5万吨(+21%)：碳酸锂产能18→21万吨/年+中国Dixin氢氧化锂厂投产，以量补价；2025年23.3万吨(+14%)：Atacama满负荷+中国硫酸锂转化放量+ESS需求，25Q3/Q4连创新高；2026Q1同比+19%满产满销</t>
+          <t>26Q2 锂盐销量纪录 84,100 吨 LCE（+59% YoY / +22% QoQ），SQM Q2 净利 $660M（+646%）。⚠️26Q1 存量 62,400 与新闻口径 ~69,000 不一致（待核）。源：SQM Q2 2026 业绩（8/19-20）</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1258,7 +1252,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>已发布待拆</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1276,7 +1270,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2023年4月投产当年爬产至10.5万吨精矿；2024年满产+超细粉回路投产，Q4创纪录7.7万吨、全年24.1万吨（近Phase 1满产27万吨/年）；2025年前两季稳于6.8万吨后因采矿承包问题Q3降至4.4万吨，2025年10月矿山停产重组（转自营+大型化设备）Q4归零、全年约18.1万吨；2026年1月底复矿爬产，Q2恢复至3.5万吨</t>
+          <t>1Q26 业绩 2026-05-15 已发（官网，创纪录利润率）；精矿产量吨数待拆 → 暂记。源：Sigma Lithium 1Q26 新闻稿</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1502,7 +1496,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2025年权益量大增主因Goulamina一期投产(2025年产出33.66万吨精矿)与Cauchari爬产(2.54→3.41万吨)；Mt Marion 2025上半年低锂价下主动减产、下半年随锂价回升恢复。</t>
+          <t>2026中报(8/28)仅分项目披露(项目口径非权益)：Cauchari碳酸锂1.9万吨/Goulamina精矿23.38万吨/蒙金锂云母精矿4.23万吨；权益合计与Mt Marion未披露</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1606,20 +1600,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T11" t="n">
+        <v>16875</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V11" t="n">
+        <v>16875</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -1628,7 +1618,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2023年Bikita两条200万吨/年产线(锂辉石7月投料、11月双达产)建成，精矿产能跃升至锂辉石30万吨+透锂长石30万吨/年；2024-2025年满产运行；2026年2月津巴布韦暂停锂精矿出口，4月获6个月出口配额恢复发运。</t>
+          <t>中报业绩交流会(8/25,巨潮披露)：H1锂精矿约30万吨(辉石21+透锂长石9,精矿原值未折LCE,未按Bikita/Tanco分拆)</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1638,7 +1628,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2023年=Bikita透锂长石精矿12万吨(折LCE约1万吨，公司口径12万吨透锂长石≈1万吨LCE)+加拿大Tanco锂辉石精矿3.2万吨(折LCE约4,000吨)，合计约1.4万吨LCE（源自2023年12月公司投资者交流纪要口径）。锂辉石精矿按SC6×0.125折LCE；透锂长石精矿品位较低(约4%)，按公司口径×0.083折。Bikita、Tanco均100%权益。 | 2024年：全年实际产量未找到公司披露——2024H1投入原料为Bikita锂辉石精矿14万吨+化学级透锂长石9万吨+技术级透锂长石1.5万吨+Tanco锂辉石2万吨(2024年业绩说明会，系H1累计投料口径非产量)；2024年初指引两矿各产30万吨。2025年：全年未找到披露——2025年前三季度Bikita产锂辉石精矿25.6万吨(Q3单季8.1万吨，中证报等引公司口径)。2026Q1未披露。2023年数值源自投资者交流纪要(雪球整理)，与公司历次公开口径一致但非公告原文，精度有限。 | 部分数值为华泰供需底稿口径(2025E含预测)</t>
+          <t>2023年=Bikita透锂长石精矿12万吨(折LCE约1万吨，公司口径12万吨透锂长石≈1万吨LCE)+加拿大Tanco锂辉石精矿3.2万吨(折LCE约4,000吨)，合计约1.4万吨LCE（源自2023年12月公司投资者交流纪要口径）。锂辉石精矿按SC6×0.125折LCE；透锂长石精矿品位较低(约4%)，按公司口径×0.083折。Bikita、Tanco均100%权益。 | 2024年：全年实际产量未找到公司披露——2024H1投入原料为Bikita锂辉石精矿14万吨+化学级透锂长石9万吨+技术级透锂长石1.5万吨+Tanco锂辉石2万吨(2024年业绩说明会，系H1累计投料口径非产量)；2024年初指引两矿各产30万吨。2025年：全年未找到披露——2025年前三季度Bikita产锂辉石精矿25.6万吨(Q3单季8.1万吨，中证报等引公司口径)。2026Q1未披露。2023年数值源自投资者交流纪要(雪球整理)，与公司历次公开口径一致但非公告原文，精度有限。 | 部分数值为华泰供需底稿口径(2025E含预测)；H1精矿约30万吨(辉石21×0.125=26,250+透锂长石9万×1/12=7,500)折LCE≈33,750（中报累计相减/折算推算），Q1未披露，两季平分拟合</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1744,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Arcadia 2023年建成投产(年处理450万吨原矿，设计年产约50万吨精矿)，2024年出货40万吨(+41%)；2026Q1年产5万吨硫酸锂项目建成试产，实现矿冶一体化；2026年2月津巴布韦出口禁令后4月获批文恢复。</t>
+          <t>2026中报(8/19)未披露Arcadia精矿量(津巴布韦2/25起禁精矿出口转本地加工)；披露碳酸锂出货量3.05万吨(+17%,销量口径含硫酸锂转化)</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -1858,20 +1848,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T13" t="n">
+        <v>9725</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V13" t="n">
+        <v>9725</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -1880,7 +1866,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>萨比星2023年5月投产，2024年放量使精矿产量同比+65%至28.60万吨；2025年29.98万吨(+4.82%)稳产；木绒锂矿(四川)推进建设中。</t>
+          <t>2026中报(8/24)：H1下属子公司锂精矿合计15.56万吨×0.125=19,450吨LCE（推算）</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -1890,7 +1876,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>年报口径「下属子公司锂精矿产量合计」(未按权益折算的并表项目产量)：2023=17.3万吨、2024=28.60万吨、2025=29.98万吨，统一×0.125(SC6)折LCE。构成：津巴布韦萨比星(原矿Li2O约1.98%，精矿产能约20万吨/年)+四川业隆沟(奥伊诺，约7.5万吨/年)；2023年萨比星5月投产当年产约10万吨。 | 2023年17.3万吨源自2023年度业绩说明会(其中萨比星约10万吨)；2024/2025为年报披露值。2026Q1：一季报未披露精矿产量，留null。折算系数0.125为统一口径，萨比星精矿实际品位约5.5-6%。</t>
+          <t>年报口径「下属子公司锂精矿产量合计」(未按权益折算的并表项目产量)：2023=17.3万吨、2024=28.60万吨、2025=29.98万吨，统一×0.125(SC6)折LCE。构成：津巴布韦萨比星(原矿Li2O约1.98%，精矿产能约20万吨/年)+四川业隆沟(奥伊诺，约7.5万吨/年)；2023年萨比星5月投产当年产约10万吨。 | 2023年17.3万吨源自2023年度业绩说明会(其中萨比星约10万吨)；2024/2025为年报披露值。2026Q1：一季报未披露精矿产量，留null。折算系数0.125为统一口径，萨比星精矿实际品位约5.5-6%。；2026中报H1精矿15.56万吨×0.125=19,450吨LCE（折算推算），Q1未披露，两季平分拟合</t>
         </is>
       </c>
     </row>
@@ -2008,7 +1994,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>自有矿从无到有：卡玛蒂维一期2024年4月投产、二期2024年11月全线投产、2025年下半年正式达产；李家沟2025年9月建成投产并达产达标；2026年2月津巴布韦出口禁令期间矿山正常生产，4月获6个月出口配额、5月恢复发运。</t>
+          <t>2026中报(8/25)无产销量绝对值(仅定性销量增长+锂业务营收49.28亿+179%)；产能锚点:锂盐近13万吨/年、卡玛蒂维精矿35万吨/年</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2120,10 +2106,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V15" t="n">
+        <v>27800</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -2132,7 +2116,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2023年阿根廷3Q盐湖投产首年0.3万吨；2024年锂价低迷主动减产近乎归零（261吨）；2025年两湖两矿（3Q、拉果错、湘源）全面建成投产+并表藏格，产量升至2.55万吨；2026Q1达1.62万吨（同比+近11倍），进入放量期。</t>
+          <t>紫金中报（8/21）：H1 当量碳酸锂 4.4 万吨；26Q2=H1−Q1=44,000−16,200=27,800 吨（推算，注明）。源：紫金矿业 2026 半年报</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2236,20 +2220,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T16" t="n">
+        <v>24700</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V16" t="n">
+        <v>24700</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -2258,7 +2238,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>蓝科锂业技改后产能由3万吨扩至4万吨/年，2024年产量4万吨（同比+10.92%）；2025年新建4万吨项目9月底投运，总产能8万吨，全年产量4.65万吨；2026年1月五矿盐湖并表后产能达9.8万吨。</t>
+          <t>2026中报(8/25)：H1碳酸锂产量4.94万吨(公司合计口径,含2026年1月起并表的五矿盐湖,未单拆蓝科)</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2268,7 +2248,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>碳酸锂实物量（即LCE），察尔汗盐湖。2023/2024年为控股子公司蓝科锂业（持股51.42%）装置100%口径；2025年4.65万吨为股份公司年报口径（蓝科4万吨+新建4万吨/年锂盐一体化项目2025年9月底投运后产出）。 | 2023年约3.6万吨（由2024年4万吨、同比+10.92%反推约3.61万吨，取3.6万吨，公司曾预计2023年产3.6万吨）。2025年前三季度产量3.16万吨（三季报/互动平台）。2026H1碳酸锂产量约4.94万吨（鑫椤资讯，实为H1累计，未填入data）。未找到2026年产量指引原文。</t>
+          <t>碳酸锂实物量（即LCE），察尔汗盐湖。2023/2024年为控股子公司蓝科锂业（持股51.42%）装置100%口径；2025年4.65万吨为股份公司年报口径（蓝科4万吨+新建4万吨/年锂盐一体化项目2025年9月底投运后产出）。 | 2023年约3.6万吨（由2024年4万吨、同比+10.92%反推约3.61万吨，取3.6万吨，公司曾预计2023年产3.6万吨）。2025年前三季度产量3.16万吨（三季报/互动平台）。2026H1碳酸锂产量约4.94万吨（鑫椤资讯，实为H1累计，未填入data）。未找到2026年产量指引原文。；2026中报H1碳酸锂4.94万吨（含五矿盐湖并表），Q1未披露，两季平分拟合</t>
         </is>
       </c>
     </row>
@@ -2362,20 +2342,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T17" t="n">
+        <v>2700</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V17" t="n">
+        <v>2700</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
@@ -2384,7 +2360,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2023年超产至约1.21万吨；2024年1.16万吨（-4.1%）；2025年7月察尔汗提锂因手续问题被责令停产整改，全年产量降至8,808吨。</t>
+          <t>2026中报(8/20)：H1碳酸锂产量5,400吨(上年同期5,170吨)；含税均价16.49万/吨</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2394,7 +2370,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>碳酸锂实物量（即LCE），察尔汗盐湖藏格锂业（1万吨/年产能，超产运行）。注：藏格矿业2025年5月起并入紫金矿业合并报表，此处为藏格自身披露口径。 | 2023年产量为约数：年报口径约1.21万吨（超额完成1.2万吨目标），未获取到精确吨数。2024年11,566吨（同比-4.1%，销量13,582吨）。2025年8,808吨（销量8,957吨，2025年报摘要）。</t>
+          <t>碳酸锂实物量（即LCE），察尔汗盐湖藏格锂业（1万吨/年产能，超产运行）。注：藏格矿业2025年5月起并入紫金矿业合并报表，此处为藏格自身披露口径。 | 2023年产量为约数：年报口径约1.21万吨（超额完成1.2万吨目标），未获取到精确吨数。2024年11,566吨（同比-4.1%，销量13,582吨）。2025年8,808吨（销量8,957吨，2025年报摘要）。；2026中报H1碳酸锂5,400吨，Q1未披露，两季平分拟合</t>
         </is>
       </c>
     </row>
@@ -2488,20 +2464,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T18" t="n">
+        <v>1131.85</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V18" t="n">
+        <v>1131.85</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -2510,7 +2482,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>一期太阳池锂精矿产量逐年收缩（0.78→0.51→0.34万吨）；二期万吨电池级碳酸锂项目（全球首套膜分离+MVR工艺）2025年9月20-24日完成120小时功能考核正式投产，2025Q4实现连续稳定出料，当年产出碳酸锂656.51吨，目前处爬坡期、产量尚不稳定。</t>
+          <t>2026中报(8/21)：一期锂精矿H1=0(太阳池工艺季节因素,预计下半年产出)；二期碳酸锂2,263.7吨(互动平台口径,爬坡期,设计1.2万吨/年)</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2520,7 +2492,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>扎布耶盐湖。原始披露：2023年锂精矿7,773.35吨；2024年锂精矿5,083.27吨；2025年锂精矿3,367.47吨+碳酸锂656.51吨。注意：扎布耶锂精矿为太阳池结晶的碳酸锂精矿（品位远高于锂辉石SC6），此处按任务统一规则将锂精矿×0.125折LCE（2023=7,773.35×0.125；2024=5,083.27×0.125；2025=3,367.47×0.125+碳酸锂656.51直接计入），折算值显著低估实际LCE，原值已列明。 | 2023/2024年报中的“锂盐生产量”经公司董秘确认均为锂精矿口径。2025年数据来自股吧转述2025年报（锂精矿3,367.47吨、碳酸锂656.51吨、氯化钾13,346吨），建议复核年报原文。万吨项目原计划2024年6月投产，实际延至2025年9月。</t>
+          <t>扎布耶盐湖。原始披露：2023年锂精矿7,773.35吨；2024年锂精矿5,083.27吨；2025年锂精矿3,367.47吨+碳酸锂656.51吨。注意：扎布耶锂精矿为太阳池结晶的碳酸锂精矿（品位远高于锂辉石SC6），此处按任务统一规则将锂精矿×0.125折LCE（2023=7,773.35×0.125；2024=5,083.27×0.125；2025=3,367.47×0.125+碳酸锂656.51直接计入），折算值显著低估实际LCE，原值已列明。 | 2023/2024年报中的“锂盐生产量”经公司董秘确认均为锂精矿口径。2025年数据来自股吧转述2025年报（锂精矿3,367.47吨、碳酸锂656.51吨、氯化钾13,346吨），建议复核年报原文。万吨项目原计划2024年6月投产，实际延至2025年9月。；2026中报：一期锂精矿H1=0+二期碳酸锂2,263.7吨，Q1未披露，两季平分拟合</t>
         </is>
       </c>
     </row>
@@ -2614,20 +2586,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T19" t="n">
+        <v>9131.25</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V19" t="n">
+        <v>9131.25</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -2636,7 +2604,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>自有45万吨/年选矿产能长期制约产出（采矿能力105万吨/年）；2024年12月与康定市政府签原矿外运协议，2025年通过外运委托选矿打破瓶颈，精矿产量暴增175%至18.56万吨，达105万吨采矿产能理论上限。</t>
+          <t>2026中报(8/17)：H1锂精矿14.61万吨(自产+委托加工合计,+108.8%;Q2单季8.67万吨)×0.125=18,262.5吨LCE（推算）</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2646,7 +2614,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>甲基卡134号脉锂辉石精矿（6%品位，SC6），按×0.125折LCE。原始吨数：2023年6.49万吨（同比+18.01%）；2024年6.75万吨（+4.07%）；2025年18.56万吨（+174.83%，含原矿外运委托选矿产出11.53万吨）。折算：64,900×0.125=8,112.5；67,500×0.125=8,437.5；185,600×0.125=23,200吨LCE。 | 精矿基本全部供应联营锂盐厂成都融捷锂业（2万吨/年锂盐产能，2025年满产）。2026Q1未披露精矿产量（仅业绩：营收3.76亿元+295.77%）。2025年采矿量/剥岩量等见年报。</t>
+          <t>甲基卡134号脉锂辉石精矿（6%品位，SC6），按×0.125折LCE。原始吨数：2023年6.49万吨（同比+18.01%）；2024年6.75万吨（+4.07%）；2025年18.56万吨（+174.83%，含原矿外运委托选矿产出11.53万吨）。折算：64,900×0.125=8,112.5；67,500×0.125=8,437.5；185,600×0.125=23,200吨LCE。 | 精矿基本全部供应联营锂盐厂成都融捷锂业（2万吨/年锂盐产能，2025年满产）。2026Q1未披露精矿产量（仅业绩：营收3.76亿元+295.77%）。2025年采矿量/剥岩量等见年报。；2026中报H1精矿14.61万吨×0.125=18,262.5吨LCE（折算推算），Q1未披露，两季平分拟合</t>
         </is>
       </c>
     </row>
@@ -2762,7 +2730,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>产量逐年小幅下滑：2023年2.71万吨→2024年约2.60万吨→2025年24,823吨（-4.7%），主因一期1万吨电池级碳酸锂产线技改（建设期约9个月）及锂价低迷主动控产。</t>
+          <t>2026中报(8/25)未披露碳酸锂吨数(碳酸锂收入19.57亿+163.59%,毛利率53.56%;券商测算勿入)</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2894,7 +2862,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026中报(8/25)仅定性'锂盐产品产销量下降'(锂板块收入4.33亿,毛利率-3.71%);茜坑矿未投产,原料外购</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -3012,14 +2980,17 @@
         <f>IF(AND(ISNUMBER(T22),ISNUMBER(N22),N22&lt;&gt;0),(T22-N22)/N22,"-")</f>
         <v/>
       </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V22" t="n">
+        <v>4157</v>
       </c>
       <c r="W22">
         <f>IF(AND(ISNUMBER(V22),ISNUMBER(O22),O22&lt;&gt;0),(V22-O22)/O22,"-")</f>
         <v/>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>26Q2 Cauchari-Olaroz 碳酸锂 9,280 吨（5 月计划检修后恢复近设计产能）×44.8% 权益=4,157 吨（推算注明）；Stage 2 +45ktpa 扩建推进。源：Lithium Argentina Q2 2026 业绩（8/11）</t>
+        </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
@@ -3122,23 +3093,24 @@
         <f>IF(AND(ISNUMBER(R23),ISNUMBER(M23),M23&lt;&gt;0),(R23-M23)/M23,"-")</f>
         <v/>
       </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T23" t="n">
+        <v>5922</v>
       </c>
       <c r="U23">
         <f>IF(AND(ISNUMBER(T23),ISNUMBER(N23),N23&lt;&gt;0),(T23-N23)/N23,"-")</f>
         <v/>
       </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V23" t="n">
+        <v>6810</v>
       </c>
       <c r="W23">
         <f>IF(AND(ISNUMBER(V23),ISNUMBER(O23),O23&lt;&gt;0),(V23-O23)/O23,"-")</f>
         <v/>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>26Q2（6 月季）NAL 精矿 54,479 dmt（+15% QoQ，5 月单月纪录 22,202t）×0.125=6,810 吨 LCE；26Q1 推算 5,922（=54,479/1.15×0.125）；FY26 197,968t。源：Elevra 6 月季报（7/28 ASX/ABN）</t>
+        </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -3252,12 +3224,17 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>未找到</t>
         </is>
       </c>
       <c r="W24">
         <f>IF(AND(ISNUMBER(V24),ISNUMBER(O24),O24&lt;&gt;0),(V24-O24)/O24,"-")</f>
         <v/>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>AMG Q2 2026 已发布但 Mibra 锂精矿分季产量未在公开快讯披露（分部口径）→ 未找到，待财报全文核。源：AMG Critical Materials Q2 2026</t>
+        </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
@@ -3360,27 +3337,28 @@
         <f>IF(AND(ISNUMBER(R25),ISNUMBER(M25),M25&lt;&gt;0),(R25-M25)/M25,"-")</f>
         <v/>
       </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T25" t="n">
+        <v>4220</v>
       </c>
       <c r="U25">
         <f>IF(AND(ISNUMBER(T25),ISNUMBER(N25),N25&lt;&gt;0),(T25-N25)/N25,"-")</f>
         <v/>
       </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V25" t="n">
+        <v>4220</v>
       </c>
       <c r="W25">
         <f>IF(AND(ISNUMBER(V25),ISNUMBER(O25),O25&lt;&gt;0),(V25-O25)/O25,"-")</f>
         <v/>
       </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Centenario H1 2026 碳酸锂 8,440 吨 LCE（销量 8,320）；Q2 平均达产 85%、后续 90%。半年口径。源：Eramet H1 2026（7/29）/Econosur</t>
+        </is>
+      </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>跨品种修正：已在镍目录（SLN/Weda Bay）；锂行仅Centenario，2024投产爬坡；2026-08-18新增骨架行，数据待回填</t>
+          <t>跨品种修正：已在镍目录（SLN/Weda Bay）；锂行仅Centenario，2024投产爬坡；2026-08-18新增骨架行，数据待回填；Centenario 2026H1碳酸锂8,440吨LCE，Q1未披露，两季平分拟合</t>
         </is>
       </c>
     </row>
@@ -3771,7 +3749,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>四川赣锋5万吨锂盐项目2024年调试完成、丰城赣锋等产能释放，产量三年连创新高（10.4→13.0→18.2万吨LCE）</t>
+          <t>2026中报(8/28)未披露合并锂盐产量折LCE(仅分基地设计产能+'量价齐升'定性)</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -3897,7 +3875,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>安居2万吨碳酸锂2023年底投产、奎纳纳一期爬坡（2025年稳定于约50%铭牌产能）、张家港3万吨氢氧化锂2025年7月竣工爬坡，产量5.07→7.07→8.79万吨逐年抬升</t>
+          <t>2026中报(8/27)未披露锂化合物及衍生品产量(仅定性销量上升,建成产能12.26万吨/年)；泰利森H1精矿73.8万吨为项目口径,勿入本行</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -4023,7 +4001,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>雅安锂业二期3万吨碳酸锂2024年投产、雅安三期及李家沟矿2025年9月达产、卡玛蒂维精矿自供放量，产量3.13→4.83→6.86万吨连续高增</t>
+          <t>2026中报(8/25)锂产品生产量未披露(同资源行)</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -4127,20 +4105,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T5" t="n">
+        <v>28250</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V5" t="n">
+        <v>28250</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -4149,7 +4123,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>印尼6万吨锂盐项目爬坡+盛新科技0.5万吨碳酸锂投产，产量5.67→6.76→7.75万吨稳步增长；2025年末已建成锂盐产能13.7万吨/年（国内7.7+印尼6）</t>
+          <t>2026中报(8/24)：H1锂产品产量5.65万吨(+68.63%;锂盐+金属锂口径,含印尼盛拓放量)；销量5.88万吨</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -4159,7 +4133,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>锂产品（锂盐，碳酸锂+氢氧化锂为主）产量，实物吨，年报口径（致远锂业/遂宁盛新/盛新科技/印尼盛拓等基地）；2025=7.75万吨(年报,同比+14.58%)；2024=6.76万吨(年报,同比+19.20%)；2023=5.67万吨(2023年报,同比+19.0%) | 三年均为年报披露值（2023/2025经年报点评及媒体转述年报原文核验）。2025年锂精矿自供产量29.98万吨；津巴布韦萨比星矿约占2026年锂盐原料需求1/3。季度值未披露</t>
+          <t>锂产品（锂盐，碳酸锂+氢氧化锂为主）产量，实物吨，年报口径（致远锂业/遂宁盛新/盛新科技/印尼盛拓等基地）；2025=7.75万吨(年报,同比+14.58%)；2024=6.76万吨(年报,同比+19.20%)；2023=5.67万吨(2023年报,同比+19.0%) | 三年均为年报披露值（2023/2025经年报点评及媒体转述年报原文核验）。2025年锂精矿自供产量29.98万吨；津巴布韦萨比星矿约占2026年锂盐原料需求1/3。季度值未披露；2026中报H1锂产品5.65万吨(+68.63%)，Q1未披露，两季平分拟合</t>
         </is>
       </c>
     </row>
@@ -4253,20 +4227,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T6" t="n">
+        <v>12500</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V6" t="n">
+        <v>12500</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -4275,7 +4245,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>中矿锂业3.5万吨高纯锂盐项目2023年11月点火、2024年2月达产，2024年产量倍增至4.37万吨；2025年受Bikita自供矿节奏及价格影响回落至3.74万吨</t>
+          <t>中报业绩会(8/25)：H1锂盐合计约2.5万吨(电池级碳酸锂约2万+氢氧化锂/氟化锂约0.5万)；6/30-7/11两条产线检修已复产</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -4285,7 +4255,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>锂盐（电池级碳酸锂/氢氧化锂/氟化锂等，江西东鹏+中矿锂业基地）生产量，实物吨；2024=43,732吨(2024年报,同比+138%)；2025=3.74万吨(2025年报,同比-14.46%)；2023=约1.84万吨(五矿证券据公告；由2024同比+138%反推18,375吨一致) | 2023年为五矿证券整理值（与同比反推一致）；2024/2025为年报披露值。现有6.6万吨/年锂盐产能，春鹏锂业3.5万吨高纯锂盐项目建成后合计418万吨/年锂精矿+7.1万吨/年电池级锂盐产能。季度值未披露</t>
+          <t>锂盐（电池级碳酸锂/氢氧化锂/氟化锂等，江西东鹏+中矿锂业基地）生产量，实物吨；2024=43,732吨(2024年报,同比+138%)；2025=3.74万吨(2025年报,同比-14.46%)；2023=约1.84万吨(五矿证券据公告；由2024同比+138%反推18,375吨一致) | 2023年为五矿证券整理值（与同比反推一致）；2024/2025为年报披露值。现有6.6万吨/年锂盐产能，春鹏锂业3.5万吨高纯锂盐项目建成后合计418万吨/年锂精矿+7.1万吨/年电池级锂盐产能。季度值未披露；中报业绩会H1锂盐约2.5万吨，Q1未披露，两季平分拟合</t>
         </is>
       </c>
     </row>
@@ -4401,7 +4371,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>眉山基地、伟能锂业、奉新时代产能爬坡，2024年大幅放量；2025年产品结构从氢氧化锂转向碳酸锂（氢氧化锂5.95万吨↓、碳酸锂4.74万吨↑），总量基本持平约10.7万吨</t>
+          <t>2026中报(8/18)产销量表为金额口径(非吨数);H1锂电材料收入73.16亿,毛利率43.84%</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -4527,7 +4497,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024年采选技改+2025年技改项目及锂价低迷下主动控量，产量自2.71万吨缓降至2.48万吨；化山瓷石矿采矿证已扩至900万吨/年，远期一体化产能约5万吨LCE</t>
+          <t>2026中报(8/25)未披露(同资源行)</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -4655,7 +4625,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024-2025年自有矿（茜坑）未投产、原料全部外购，成本高企下锂盐产线阶段性检修减产，产量1.55→1.36万吨；2026年计划云母产线适时点火、逐步全线满产</t>
+          <t>2026中报(8/25)未披露(同资源行;2025年报锂盐生产量13,610吨为最近锚点)</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -4785,7 +4755,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>成都融捷锂业2万吨/年产线2023年起爬坡，2025年借甲基卡105万吨采矿放量（锂精矿18.56万吨，+174.83%）实现满产；2025年成都融捷锂业净利润2.16亿元</t>
+          <t>2026中报(8/17)联营成都融捷锂业仅披露H1净利4.40亿+'产销量大幅增长'定性,无吨数(公司精矿98.97%售往该联营厂)</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -4914,7 +4884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5024,6 +4994,40 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>锂 26Q2 欠账补录：PLS 26,788 / MinRes 22,000 / SQM 84,100（销量纪录）/ Lithium Argentina 4,157（权益推算）/ Elevra 6,810 / 紫金 27,800（推算）；Sigma 待拆；AMG 未找到；Eramet Centenario H1=8440</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>PLS/MinRes Q4FY26 季报（7/29）；SQM Q2（8/19）；LAR Q2（8/11）；Elevra 6 月季（7/28）；Eramet H1（7/29）；紫金中报（8/21）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>锂 26Q2 中报回填：可入库=盛新(资源H1=19450折算/冶炼H1=56500)、中矿(精矿约30万吨原值/锂盐H1=25000)、盐湖H1=49400、藏格H1=5400、西藏矿业H1=2263.7(一期0+二期碳酸锂)、融捷H1=18262.5折算；未披露=赣锋/天齐/雅化/天华/永兴/江特/华友(均中报原文+转载核实无吨数)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>各公司2026中报(巨潮/新浪全文)+中矿8/25业绩交流会纪要(巨潮)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/excel/锂.xlsx
+++ b/excel/锂.xlsx
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>权益口径合计（推算）：①Mt Marion(赣锋50%)：日历年混合品位精矿(约SC4.5)折SC6(×0.718，MRL披露FY26前三季46.8万吨混合=33.6万吨SC6)再×0.125折LCE。日历年产量(100%)：2024=61.2万吨(Q1 18.2万/Q2 17.8万/Q3 13.6万/Q4 11.6万，部分由MRL季报50%口径×2及环比/同比增速反推)；2025=57.2万吨(Q1 14.0/Q2 12.4/Q3 14.6/Q4 16.2万吨，MRL季报)。②Goulamina(现权益65%)：2025年产精矿33.66万吨(干，100%项目口径，赣锋2025年报)×0.125×65%。③Cauchari-Olaroz(46.67%)：碳酸锂2024=2.54万吨、2025=3.41万吨(100%，Lithium Argentina/赣锋年报)×46.67%。Mariana 2025年2月一期2万吨氯化锂投产，爬坡量未披露，未计入。 | 推算值：2024/2025为各项目权益量加总，Marion部分季度由MRL披露的50%口径×2及同比/环比增速反推，SC6折算比例0.718为FY26前三季实际值；2023年留null——Cauchari 2023年产碳酸锂约6,000吨(100%，Lithium Argentina)，Mt Marion FY23(2022/7-2023/6)产精矿23.4万吨(50%权益口径，MRL)，日历年逐季未完整核实故不汇总。2026Q1：Mt Marion产精矿16.0万吨(100%，由FY26前三季46.8万-Q3'25 14.6万-Q4'25 16.2万推得)，Cauchari/Goulamina季度未获，不汇总。2026Q2：MRL季报( FY26Q4 )预计7月底发布，截至7/28未发布。</t>
+          <t>权益口径合计（推算）：①Mt Marion(赣锋50%)：日历年混合品位精矿(约SC4.5)折SC6(×0.718，MRL披露FY26前三季46.8万吨混合=33.6万吨SC6)再×0.125折LCE。日历年产量(100%)：2024=61.2万吨(Q1 18.2万/Q2 17.8万/Q3 13.6万/Q4 11.6万，部分由MRL季报50%口径×2及环比/同比增速反推)；2025=57.2万吨(Q1 14.0/Q2 12.4/Q3 14.6/Q4 16.2万吨，MRL季报)。②Goulamina(现权益65%)：2025年产精矿33.66万吨(干，100%项目口径，赣锋2025年报)×0.125×65%。③Cauchari-Olaroz(46.67%)：碳酸锂2024=2.54万吨、2025=3.41万吨(100%，Lithium Argentina/赣锋年报)×46.67%。Mariana 2025年2月一期2万吨氯化锂投产，爬坡量未披露，未计入。 | 推算值：2024/2025为各项目权益量加总，Marion部分季度由MRL披露的50%口径×2及同比/环比增速反推，SC6折算比例0.718为FY26前三季实际值；2023年留null——Cauchari 2023年产碳酸锂约6,000吨(100%，Lithium Argentina)，Mt Marion FY23(2022/7-2023/6)产精矿23.4万吨(50%权益口径，MRL)，日历年逐季未完整核实故不汇总。2026Q1：Mt Marion产精矿16.0万吨(100%，由FY26前三季46.8万-Q3'25 14.6万-Q4'25 16.2万推得)，Cauchari/Goulamina季度未获，不汇总。2026Q2：MRL季报( FY26Q4 )预计7月底发布，截至7/28未发布。｜2026Q2分项目(项目口径，权益合计因Goulamina无季度拆分仍不汇总)：Mt Marion产精矿82k dmt(50%权益基准，100%≈16.4万吨，回收率59%，MRL Q4FY26季报7/29)；Cauchari产碳酸锂9,280吨(LAR Q2季报8/11，与赣锋中报H1=1.9万吨一致)；Goulamina H1=23.38万吨精矿(中报)无季度拆分(2026-10-14补)</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5028,6 +5028,23 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>26Q2复核：锂资源/冶炼11行中报核查结论(8月批次)复核成立——永兴/雅化/赣锋/天齐抽查一致（中报均无产量吨数）；赣锋资源行备注补Mt Marion 26Q2=82k dmt(50%基准,MRL 7/29)+Cauchari 9,280吨(LAR 8/11)项目口径值，权益合计因Goulamina无季度拆分仍不汇总</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>MRL Q4FY26 Quarterly Activity Report；Lithium Argentina Q2 2026 Results；各公司2026中报</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
